--- a/assets/showcase/dashboard.xlsx
+++ b/assets/showcase/dashboard.xlsx
@@ -8,7 +8,9 @@
   <x:sheets>
     <x:sheet name="Dashboard" sheetId="1" r:id="rId2"/>
   </x:sheets>
-  <x:definedNames/>
+  <x:definedNames>
+    <x:definedName name="_xlnm.Print_Area" localSheetId="0">Dashboard!$B$2:$J$54</x:definedName>
+  </x:definedNames>
   <x:calcPr calcId="125725"/>
 </x:workbook>
 </file>
@@ -1320,6 +1322,7 @@
 <x:worksheet xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
+    <x:pageSetUpPr fitToPage="1"/>
   </x:sheetPr>
   <x:dimension ref="A1"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
@@ -1866,7 +1869,7 @@
   </x:conditionalFormatting>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
-  <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
+  <x:pageSetup paperSize="1" fitToHeight="0" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
   <x:headerFooter/>
   <x:drawing r:id="Rd13d540bc92545d5"/>
   <x:tableParts count="0"/>
@@ -1933,6 +1936,21 @@
           </x14:cfRule>
           <xm:sqref>I10:I17</xm:sqref>
         </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{02949277-19B2-4EF6-841D-0E7A7BEB03F1}">
+            <x14:dataBar minLength="0" maxLength="100" showValue="1" gradient="1">
+              <x14:cfvo type="num">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:negativeFillColor rgb="FF38BDF8"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>I10:I17</xm:sqref>
+        </x14:conditionalFormatting>
       </x14:conditionalFormattings>
     </x:ext>
   </x:extLst>
